--- a/02_DIA_inicio_2026_analisis_assets/rbd_9720_colegio-hernan-olguin_nt2_rubricas.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9720_colegio-hernan-olguin_nt2_rubricas.xlsx
@@ -1992,13 +1992,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DEC6372E-9D15-4AFC-B4A1-B16CCFE70EAE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83DD3FB3-0307-4A8F-8605-551DE0B317FB}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A6983B83-D97C-474C-8296-6DE0F63182A0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CCE93B64-E2E1-4C31-849A-F945497B2AEB}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25214008-6B71-440D-85CA-359B42871314}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BEC9A7A9-80A9-4874-84C9-EEDBC73523D3}"/>
 </file>